--- a/assistant/matrix/Assistant-Overview.xlsx
+++ b/assistant/matrix/Assistant-Overview.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\inetsoft\test-garden\assistant\matrix\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="2680" yWindow="1500" windowWidth="28240" windowHeight="17440" xr2:uid="{752BAC88-3D22-6345-9E5D-6A586CA68B77}"/>
+    <workbookView xWindow="2685" yWindow="1500" windowWidth="28245" windowHeight="17445" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="ToDoList" sheetId="1" r:id="rId1"/>
@@ -17,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="145">
   <si>
     <t>1. 抽取Asssitant-chat的文档, 补充所有的matrix</t>
   </si>
@@ -301,15 +306,15 @@
     <r>
       <rPr>
         <b/>
+        <sz val="10"/>
         <rFont val="default"/>
-        <sz val="10"/>
       </rPr>
-      <t xml:space="preserve">·</t>
+      <t>·</t>
     </r>
     <r>
       <rPr>
+        <sz val="10"/>
         <rFont val="default"/>
-        <sz val="10"/>
       </rPr>
       <t xml:space="preserve"> chat gpt 要经历几次的调用? 每次的调用是否合理?</t>
     </r>
@@ -318,49 +323,49 @@
     <r>
       <rPr>
         <b/>
+        <sz val="10"/>
         <rFont val="default"/>
-        <sz val="10"/>
       </rPr>
       <t xml:space="preserve">· </t>
     </r>
     <r>
       <rPr>
+        <sz val="10"/>
         <rFont val="default"/>
-        <sz val="10"/>
       </rPr>
-      <t xml:space="preserve">chat gpt 每次执行的时候, 前后携带的prompt到底有多大? 存在哪些影响?</t>
+      <t>chat gpt 每次执行的时候, 前后携带的prompt到底有多大? 存在哪些影响?</t>
     </r>
   </si>
   <si>
     <r>
       <rPr>
         <b/>
+        <sz val="10"/>
         <rFont val="default"/>
-        <sz val="10"/>
       </rPr>
       <t xml:space="preserve">· </t>
     </r>
     <r>
       <rPr>
+        <sz val="10"/>
         <rFont val="default"/>
-        <sz val="10"/>
       </rPr>
-      <t xml:space="preserve">一次常规问题花费的token以及时间, 是否有优化的空间</t>
+      <t>一次常规问题花费的token以及时间, 是否有优化的空间</t>
     </r>
   </si>
   <si>
     <r>
       <rPr>
         <b/>
+        <sz val="10"/>
         <rFont val="default"/>
-        <sz val="10"/>
       </rPr>
       <t xml:space="preserve">· </t>
     </r>
     <r>
       <rPr>
+        <sz val="10"/>
         <rFont val="default"/>
-        <sz val="10"/>
       </rPr>
       <t xml:space="preserve"> Rerank的次数和花费</t>
     </r>
@@ -393,233 +398,144 @@
     <t>3.如何区分哪些是已经store了的哪些是没有store的？</t>
   </si>
   <si>
-    <t>一、docker上的部署</t>
-  </si>
-  <si>
-    <t>see assistant\chat-app\docker\docker-compose.prod.yml</t>
-  </si>
-  <si>
-    <t>Note:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.docker-compose.yml 测试环境, 将client也作为一个容器打入. 生产环境中, client在stylebi上, 只需server和portal就可以, </t>
-  </si>
-  <si>
-    <t>2. 目前protal向server发的请求 需要授权, 但是portal有单独的授权机制, 还没有做. 暂时通过api区分, 不进行授权.</t>
-  </si>
-  <si>
-    <t>二、云上的部署</t>
+    <t>一、知识库的生命周期管理：喂养与优化</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.日常运营：审核与沉淀流程的持续执行   </t>
+  </si>
+  <si>
+    <t>定义从“审核通过的优质问答”到“正式入库成为知识库文章”的标准化流程和责任人</t>
+  </si>
+  <si>
+    <t>a.审核员打开一条待审记录，需要快速判断其类型：</t>
+  </si>
+  <si>
+    <t>A. 知识缺口型：AI不知道答案（如关于一个冷门功能）。→ 需要创建新知识。</t>
+  </si>
+  <si>
+    <t>B. 知识不准型：AI给出了错误或过时的信息。→ 需要修正已有知识。</t>
+  </si>
+  <si>
+    <t>C. 表达不佳型：AI知道答案，但解释得复杂、晦涩或未切中要害。→ 需要优化表达或提供更佳范例。</t>
+  </si>
+  <si>
+    <t>D. 无效/无关型：用户提问不清晰、或问题与产品无关。→ 可关闭，不沉淀。</t>
+  </si>
+  <si>
+    <t>b.专家审核 (Knowledge Curator Review):</t>
+  </si>
+  <si>
+    <t>未经审查的“草稿”不能直接喂给AI，需要一道质量关卡</t>
+  </si>
+  <si>
+    <t>由指定的产品经理或领域专家，对审核员提交的“知识草稿”进行最终审阅。</t>
   </si>
   <si>
     <r>
       <rPr>
         <b/>
         <sz val="10"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
       </rPr>
-      <t xml:space="preserve">方案一：</t>
+      <t>检查项：</t>
     </r>
     <r>
       <rPr>
+        <sz val="10"/>
         <color theme="1"/>
         <rFont val="等线"/>
-        <sz val="10"/>
+        <family val="3"/>
+        <charset val="134"/>
       </rPr>
-      <t xml:space="preserve">全托管容器服务（推荐起点，平衡简单与可控）</t>
+      <t>准确性、完整性、清晰度、格式规范性、是否符合产品最新版本。</t>
     </r>
-  </si>
-  <si>
-    <t>这是目前最主流、最推荐的方式。将应用打包成Docker容器，利用云平台的容器托管服务运行。</t>
-  </si>
-  <si>
-    <t>代表服务：</t>
-  </si>
-  <si>
-    <t>AWS: Elastic Container Service (ECS) 或 Fargate（无服务器容器）</t>
-  </si>
-  <si>
-    <t>Azure: Azure Container Instances (ACI) 或 Azure Kubernetes Service (AKS)</t>
-  </si>
-  <si>
-    <t>Google Cloud: Google Kubernetes Engine (GKE) 或 Cloud Run（无服务器容器）</t>
-  </si>
-  <si>
-    <t>阿里云: 弹性容器实例 (ECI) 或 容器服务 Kubernetes 版 (ACK)</t>
-  </si>
-  <si>
-    <t>腾讯云: 弹性容器服务 (EKS) 或 云原生 Serverless 容器</t>
-  </si>
-  <si>
-    <t>部署流程：</t>
-  </si>
-  <si>
-    <t>1.容器化：将你们的AI助手后端代码（含RAG逻辑、Prompt工程等）编写Dockerfile，打包成镜像。</t>
-  </si>
-  <si>
-    <t>2.上传镜像：将镜像推送到云平台的容器镜像仓库（如ECR, ACR）。</t>
-  </si>
-  <si>
-    <t>3.配置服务：在托管控制台定义服务：</t>
-  </si>
-  <si>
-    <t>任务定义/Deployment：指定镜像、CPU/内存、环境变量（OPENAI_API_KEY, PINECONE_API_KEY等）。</t>
-  </si>
-  <si>
-    <t>网络：配置VPC、安全组，通常不需要公网IP（仅前端能访问即可）。</t>
-  </si>
-  <si>
-    <t>负载均衡：创建ALB/NLB将流量分发给多个容器实例。</t>
-  </si>
-  <si>
-    <t>4.发布与扩缩容：一键部署。设置基于CPU/内存使用率的自动扩缩容策略。</t>
-  </si>
-  <si>
-    <t>优点：</t>
-  </si>
-  <si>
-    <t>高度可控：完整掌控运行时环境和应用配置。</t>
-  </si>
-  <si>
-    <t>良好的可移植性：Docker镜像可在任何云平台运行，避免供应商深度锁定。</t>
-  </si>
-  <si>
-    <t>弹性伸缩：可根据负载自动增加/减少容器实例，应对流量高峰。</t>
-  </si>
-  <si>
-    <t>成熟的CI/CD：容易与GitHub Actions, GitLab CI等集成，实现自动化构建、测试和部署。</t>
-  </si>
-  <si>
-    <t>缺点：</t>
-  </si>
-  <si>
-    <t>需要一定的容器化和运维知识。</t>
-  </si>
-  <si>
-    <t>比纯Serverless方案成本略高（需要持续运行至少1个实例）。</t>
-  </si>
-  <si>
-    <t>一、知识库的生命周期管理：喂养与优化</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.日常运营：审核与沉淀流程的持续执行   </t>
-  </si>
-  <si>
-    <t>定义从“审核通过的优质问答”到“正式入库成为知识库文章”的标准化流程和责任人</t>
-  </si>
-  <si>
-    <t>a.审核员打开一条待审记录，需要快速判断其类型：</t>
-  </si>
-  <si>
-    <t>A. 知识缺口型：AI不知道答案（如关于一个冷门功能）。→ 需要创建新知识。</t>
-  </si>
-  <si>
-    <t>B. 知识不准型：AI给出了错误或过时的信息。→ 需要修正已有知识。</t>
-  </si>
-  <si>
-    <t>C. 表达不佳型：AI知道答案，但解释得复杂、晦涩或未切中要害。→ 需要优化表达或提供更佳范例。</t>
-  </si>
-  <si>
-    <t>D. 无效/无关型：用户提问不清晰、或问题与产品无关。→ 可关闭，不沉淀。</t>
-  </si>
-  <si>
-    <t>b.专家审核 (Knowledge Curator Review):</t>
-  </si>
-  <si>
-    <t>未经审查的“草稿”不能直接喂给AI，需要一道质量关卡</t>
-  </si>
-  <si>
-    <t>由指定的产品经理或领域专家，对审核员提交的“知识草稿”进行最终审阅。</t>
   </si>
   <si>
     <r>
       <rPr>
         <b/>
         <sz val="10"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
       </rPr>
-      <t xml:space="preserve">检查项：</t>
+      <t>标准化：</t>
     </r>
     <r>
       <rPr>
+        <sz val="10"/>
         <color theme="1"/>
         <rFont val="等线"/>
-        <sz val="10"/>
+        <family val="3"/>
+        <charset val="134"/>
       </rPr>
-      <t xml:space="preserve">准确性、完整性、清晰度、格式规范性、是否符合产品最新版本。</t>
+      <t>确保风格统一（例如，所有操作指南都以“导航到... &gt; 点击... &gt; 输入...”的句式），术语一致。</t>
     </r>
+  </si>
+  <si>
+    <t>2.主动知识管理</t>
+  </si>
+  <si>
+    <t>分析高频问题：每周/月查看用户最常搜索和提问的关键词。这些是知识的“热点”。</t>
+  </si>
+  <si>
+    <t>填补知识缺口：对高频但AI解决率低的问题，主动创建或补充知识文档，而不是被动等待用户点踩。</t>
+  </si>
+  <si>
+    <t>修剪知识库：定期（如每季度）审计知识库，归档或删除过时、低质量、从未被检索到的“冷知识”，保持知识库的精炼和检索效率。</t>
+  </si>
+  <si>
+    <t>版本同步：每当产品发布新版本，必须同步更新相关功能的知识文档。这是防止AI“幻觉”和提供错误信息的关键。</t>
+  </si>
+  <si>
+    <t>二、AI提示词的持续调优：变得更聪明</t>
+  </si>
+  <si>
+    <t>1.持续基于案例优化，定期提示词评审</t>
+  </si>
+  <si>
+    <t>2.质量评估体系</t>
+  </si>
+  <si>
+    <t>建立黄金测试集：构建一个包含100-200个核心问题的“标准答案”测试集，更换模型或者prompt更新后运行，量化评估AI回答的准确率、有用性和安全性得分。</t>
+  </si>
+  <si>
+    <t>人工盲测：定期抽样一批用户真实问题，让领域专家对AI的回答和人工最佳答案进行打分。</t>
+  </si>
+  <si>
+    <t>抽样审查机制：定期随机抽取问题</t>
+  </si>
+  <si>
+    <t>三、模型与供应商管理</t>
+  </si>
+  <si>
+    <t>1.成本与用量监控</t>
+  </si>
+  <si>
+    <t>监控指标：</t>
   </si>
   <si>
     <r>
       <rPr>
         <b/>
         <sz val="10"/>
-      </rPr>
-      <t xml:space="preserve">标准化：</t>
-    </r>
-    <r>
-      <rPr>
-        <color theme="1"/>
         <rFont val="等线"/>
-        <sz val="10"/>
-      </rPr>
-      <t xml:space="preserve">确保风格统一（例如，所有操作指南都以“导航到... &gt; 点击... &gt; 输入...”的句式），术语一致。</t>
-    </r>
-  </si>
-  <si>
-    <t>2.主动知识管理</t>
-  </si>
-  <si>
-    <t>分析高频问题：每周/月查看用户最常搜索和提问的关键词。这些是知识的“热点”。</t>
-  </si>
-  <si>
-    <t>填补知识缺口：对高频但AI解决率低的问题，主动创建或补充知识文档，而不是被动等待用户点踩。</t>
-  </si>
-  <si>
-    <t>修剪知识库：定期（如每季度）审计知识库，归档或删除过时、低质量、从未被检索到的“冷知识”，保持知识库的精炼和检索效率。</t>
-  </si>
-  <si>
-    <t>版本同步：每当产品发布新版本，必须同步更新相关功能的知识文档。这是防止AI“幻觉”和提供错误信息的关键。</t>
-  </si>
-  <si>
-    <t>二、AI提示词的持续调优：变得更聪明</t>
-  </si>
-  <si>
-    <t>1.持续基于案例优化，定期提示词评审</t>
-  </si>
-  <si>
-    <t>2.质量评估体系</t>
-  </si>
-  <si>
-    <t>建立黄金测试集：构建一个包含100-200个核心问题的“标准答案”测试集，更换模型或者prompt更新后运行，量化评估AI回答的准确率、有用性和安全性得分。</t>
-  </si>
-  <si>
-    <t>人工盲测：定期抽样一批用户真实问题，让领域专家对AI的回答和人工最佳答案进行打分。</t>
-  </si>
-  <si>
-    <t>抽样审查机制：定期随机抽取问题</t>
-  </si>
-  <si>
-    <t>三、模型与供应商管理</t>
-  </si>
-  <si>
-    <t>1.成本与用量监控</t>
-  </si>
-  <si>
-    <t>监控指标：</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
+        <family val="3"/>
+        <charset val="134"/>
       </rPr>
       <t xml:space="preserve">· </t>
     </r>
     <r>
       <rPr>
+        <sz val="10"/>
         <color theme="1"/>
         <rFont val="等线"/>
-        <sz val="10"/>
+        <family val="3"/>
+        <charset val="134"/>
       </rPr>
-      <t xml:space="preserve">每日/月Token消耗量</t>
+      <t>每日/月Token消耗量</t>
     </r>
   </si>
   <si>
@@ -627,16 +543,21 @@
       <rPr>
         <b/>
         <sz val="10"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
       </rPr>
       <t xml:space="preserve">· </t>
     </r>
     <r>
       <rPr>
+        <sz val="10"/>
         <color theme="1"/>
         <rFont val="等线"/>
-        <sz val="10"/>
+        <family val="3"/>
+        <charset val="134"/>
       </rPr>
-      <t xml:space="preserve">各模型调用比例和成本</t>
+      <t>各模型调用比例和成本</t>
     </r>
   </si>
   <si>
@@ -644,16 +565,21 @@
       <rPr>
         <b/>
         <sz val="10"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
       </rPr>
       <t xml:space="preserve">· </t>
     </r>
     <r>
       <rPr>
+        <sz val="10"/>
         <color theme="1"/>
         <rFont val="等线"/>
-        <sz val="10"/>
+        <family val="3"/>
+        <charset val="134"/>
       </rPr>
-      <t xml:space="preserve">平均响应时间</t>
+      <t>平均响应时间</t>
     </r>
   </si>
   <si>
@@ -661,14 +587,19 @@
       <rPr>
         <b/>
         <sz val="10"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
       </rPr>
-      <t xml:space="preserve">·</t>
+      <t>·</t>
     </r>
     <r>
       <rPr>
+        <sz val="10"/>
         <color theme="1"/>
         <rFont val="等线"/>
-        <sz val="10"/>
+        <family val="3"/>
+        <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> 失败率和重试率</t>
     </r>
@@ -699,13 +630,17 @@
   </si>
   <si>
     <t>2.模型不可用时，自动切换到备用模型</t>
+  </si>
+  <si>
+    <t>//refer to test-garden\assistant\docs\DEPLOYMENT.md</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="18">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -722,15 +657,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="10"/>
-      <color theme="10"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="等线"/>
@@ -740,14 +666,20 @@
     </font>
     <font>
       <sz val="10"/>
+      <name val="等线"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
+      <name val="等线"/>
+      <charset val="134"/>
     </font>
     <font>
       <i/>
       <sz val="10"/>
+      <name val="等线"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
@@ -793,6 +725,29 @@
       <sz val="10"/>
       <color rgb="FFFE0300"/>
       <name val="default"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -958,149 +913,140 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="超链接" xfId="1" builtinId="8"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1409,41 +1355,41 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F1E1092-59D6-0841-9542-AE5505D0AA25}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.9990234375" defaultRowHeight="16.5" customHeight="1"/>
+  <dimension ref="B2:C9"/>
+  <sheetFormatPr defaultColWidth="10" defaultRowHeight="16.5" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="5.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="16.5" customHeight="1">
-      <c r="B2" s="4" t="s">
+    <row r="2" spans="2:3" ht="16.5" customHeight="1">
+      <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" ht="16.5" customHeight="1">
-      <c r="B3" s="4" t="s">
+    <row r="3" spans="2:3" ht="16.5" customHeight="1">
+      <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" ht="16.5" customHeight="1">
-      <c r="C4" s="4" t="s">
+    <row r="4" spans="2:3" ht="16.5" customHeight="1">
+      <c r="C4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" ht="16.5" customHeight="1">
-      <c r="B7" s="4" t="s">
+    <row r="7" spans="2:3" ht="16.5" customHeight="1">
+      <c r="B7" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="9" ht="16.5" customHeight="1">
-      <c r="B9" s="4" t="s">
+    <row r="9" spans="2:3" ht="16.5" customHeight="1">
+      <c r="B9" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1454,592 +1400,592 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F1E1092-59D6-0841-9542-AE5505D0AA25}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.9990234375" defaultRowHeight="16.5" customHeight="1"/>
+  <dimension ref="A2:N77"/>
+  <sheetFormatPr defaultColWidth="10" defaultRowHeight="16.5" customHeight="1"/>
   <sheetData>
-    <row r="2" ht="16.5" customHeight="1">
-      <c r="A2" s="10" t="s">
+    <row r="2" spans="1:12" ht="16.5" customHeight="1">
+      <c r="A2" s="7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="16.5" customHeight="1">
-      <c r="A3" s="9" t="s">
+    <row r="3" spans="1:12" ht="16.5" customHeight="1">
+      <c r="A3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="10" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" ht="81.75" customHeight="1">
-      <c r="B4" s="5" t="s">
+    <row r="4" spans="1:12" ht="81.75" customHeight="1">
+      <c r="B4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="41" t="s">
+      <c r="C4" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="I4" s="8"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
-    </row>
-    <row r="5" ht="16.5" customHeight="1">
-      <c r="B5" s="5"/>
-      <c r="C5" s="5" t="s">
+      <c r="I4" s="5"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+    </row>
+    <row r="5" spans="1:12" ht="16.5" customHeight="1">
+      <c r="B5" s="2"/>
+      <c r="C5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="8"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-    </row>
-    <row r="6" ht="16.5" customHeight="1">
-      <c r="C6" s="9" t="s">
+      <c r="I5" s="5"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+    </row>
+    <row r="6" spans="1:12" ht="16.5" customHeight="1">
+      <c r="C6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="E6" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" ht="16.5" customHeight="1">
-      <c r="C7" s="9" t="s">
+    <row r="7" spans="1:12" ht="16.5" customHeight="1">
+      <c r="C7" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="24" t="s">
+      <c r="E7" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="G7" s="11" t="s">
+      <c r="G7" s="8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="8" ht="16.5" customHeight="1">
-      <c r="G8" s="11" t="s">
+    <row r="8" spans="1:12" ht="16.5" customHeight="1">
+      <c r="G8" s="8" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="9" ht="16.5" customHeight="1">
-      <c r="E9" s="24"/>
-      <c r="G9" s="9" t="s">
+    <row r="9" spans="1:12" ht="16.5" customHeight="1">
+      <c r="E9" s="21"/>
+      <c r="G9" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="10" ht="27.75" customHeight="1">
-      <c r="E10" s="5"/>
-      <c r="G10" s="42" t="s">
+    <row r="10" spans="1:12" ht="27.75" customHeight="1">
+      <c r="E10" s="2"/>
+      <c r="G10" s="39" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="11" ht="16.5" customHeight="1">
-      <c r="E11" s="24"/>
-    </row>
-    <row r="12" ht="16.5" customHeight="1">
-      <c r="C12" s="9" t="s">
+    <row r="11" spans="1:12" ht="16.5" customHeight="1">
+      <c r="E11" s="21"/>
+    </row>
+    <row r="12" spans="1:12" ht="16.5" customHeight="1">
+      <c r="C12" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E12" s="24" t="s">
+      <c r="E12" s="21" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="14" ht="16.5" customHeight="1">
-      <c r="A14" s="9" t="s">
+    <row r="14" spans="1:12" ht="16.5" customHeight="1">
+      <c r="A14" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="J14" s="9" t="s">
+      <c r="J14" s="6" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="15" ht="16.5" customHeight="1">
-      <c r="K15" s="11"/>
-    </row>
-    <row r="16" ht="16.5" customHeight="1">
-      <c r="A16" s="10" t="s">
+    <row r="15" spans="1:12" ht="16.5" customHeight="1">
+      <c r="K15" s="8"/>
+    </row>
+    <row r="16" spans="1:12" ht="16.5" customHeight="1">
+      <c r="A16" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="K16" s="11"/>
-    </row>
-    <row r="17" ht="16.5" customHeight="1">
-      <c r="A17" s="9" t="s">
+      <c r="K16" s="8"/>
+    </row>
+    <row r="17" spans="1:13" ht="16.5" customHeight="1">
+      <c r="A17" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="K17" s="11" t="s">
+      <c r="K17" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="M17" s="11" t="s">
+      <c r="M17" s="8" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="19" ht="16.5" customHeight="1">
-      <c r="A19" s="10" t="s">
+    <row r="19" spans="1:13" ht="16.5" customHeight="1">
+      <c r="A19" s="7" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="20" ht="16.5" customHeight="1">
-      <c r="A20" s="9" t="s">
+    <row r="20" spans="1:13" ht="16.5" customHeight="1">
+      <c r="A20" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E20" s="12" t="s">
+      <c r="E20" s="9" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="21" ht="16.5" customHeight="1">
-      <c r="B21" s="9" t="s">
+    <row r="21" spans="1:13" ht="16.5" customHeight="1">
+      <c r="B21" s="6" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="22" ht="16.5" customHeight="1">
-      <c r="B22" s="9" t="s">
+    <row r="22" spans="1:13" ht="16.5" customHeight="1">
+      <c r="B22" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="H22" s="13" t="s">
+      <c r="H22" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="23" ht="16.5" customHeight="1">
-      <c r="C23" s="9" t="s">
+    <row r="23" spans="1:13" ht="16.5" customHeight="1">
+      <c r="C23" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="F23" s="11" t="s">
+      <c r="F23" s="8" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="24" ht="16.5" customHeight="1">
-      <c r="C24" s="9" t="s">
+    <row r="24" spans="1:13" ht="16.5" customHeight="1">
+      <c r="C24" s="6" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="25" ht="16.5" customHeight="1">
-      <c r="C25" s="9" t="s">
+    <row r="25" spans="1:13" ht="16.5" customHeight="1">
+      <c r="C25" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D25" s="9" t="s">
+      <c r="D25" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="I25" s="11" t="s">
+      <c r="I25" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="M25" s="11" t="s">
+      <c r="M25" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="26" ht="16.5" customHeight="1">
-      <c r="C26" s="14" t="s">
+    <row r="26" spans="1:13" ht="16.5" customHeight="1">
+      <c r="C26" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="D26" s="15"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="15"/>
-      <c r="G26" s="15"/>
-      <c r="H26" s="15"/>
-      <c r="I26" s="15"/>
-      <c r="J26" s="15"/>
-      <c r="K26" s="15"/>
-      <c r="L26" s="16"/>
-    </row>
-    <row r="27" ht="16.5" customHeight="1">
-      <c r="C27" s="17" t="s">
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="12"/>
+      <c r="H26" s="12"/>
+      <c r="I26" s="12"/>
+      <c r="J26" s="12"/>
+      <c r="K26" s="12"/>
+      <c r="L26" s="13"/>
+    </row>
+    <row r="27" spans="1:13" ht="16.5" customHeight="1">
+      <c r="C27" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="D27" s="18"/>
-      <c r="E27" s="18"/>
-      <c r="L27" s="19"/>
-    </row>
-    <row r="28" ht="16.5" customHeight="1">
-      <c r="C28" s="17" t="s">
+      <c r="D27" s="15"/>
+      <c r="E27" s="15"/>
+      <c r="L27" s="16"/>
+    </row>
+    <row r="28" spans="1:13" ht="16.5" customHeight="1">
+      <c r="C28" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="E28" s="18" t="s">
+      <c r="E28" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="I28" s="18" t="s">
+      <c r="I28" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="L28" s="20" t="s">
+      <c r="L28" s="17" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="29" ht="16.5" customHeight="1">
-      <c r="C29" s="21" t="s">
+    <row r="29" spans="1:13" ht="16.5" customHeight="1">
+      <c r="C29" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="E29" s="22" t="s">
+      <c r="E29" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="I29" s="22" t="s">
+      <c r="I29" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="L29" s="19" t="s">
+      <c r="L29" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="M29" s="23"/>
-    </row>
-    <row r="30" ht="16.5" customHeight="1">
-      <c r="C30" s="21"/>
-      <c r="E30" s="22"/>
-      <c r="I30" s="22" t="s">
+      <c r="M29" s="20"/>
+    </row>
+    <row r="30" spans="1:13" ht="16.5" customHeight="1">
+      <c r="C30" s="18"/>
+      <c r="E30" s="19"/>
+      <c r="I30" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="L30" s="19" t="s">
+      <c r="L30" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="M30" s="24" t="s">
+      <c r="M30" s="21" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="31" ht="16.5" customHeight="1">
-      <c r="C31" s="21" t="s">
+    <row r="31" spans="1:13" ht="16.5" customHeight="1">
+      <c r="C31" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="E31" s="22" t="s">
+      <c r="E31" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="I31" s="22" t="s">
+      <c r="I31" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="L31" s="25" t="s">
+      <c r="L31" s="22" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="32" ht="16.5" customHeight="1">
-      <c r="C32" s="26"/>
-      <c r="L32" s="19"/>
-      <c r="M32" s="23"/>
-    </row>
-    <row r="33" ht="16.5" customHeight="1">
-      <c r="C33" s="27" t="s">
+    <row r="32" spans="1:13" ht="16.5" customHeight="1">
+      <c r="C32" s="23"/>
+      <c r="L32" s="16"/>
+      <c r="M32" s="20"/>
+    </row>
+    <row r="33" spans="3:14" ht="16.5" customHeight="1">
+      <c r="C33" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="L33" s="19"/>
-      <c r="M33" s="23"/>
-    </row>
-    <row r="34" ht="16.5" customHeight="1">
-      <c r="C34" s="28" t="s">
+      <c r="L33" s="16"/>
+      <c r="M33" s="20"/>
+    </row>
+    <row r="34" spans="3:14" ht="16.5" customHeight="1">
+      <c r="C34" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="E34" s="23" t="s">
+      <c r="E34" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="I34" s="23" t="s">
+      <c r="I34" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="L34" s="20" t="s">
+      <c r="L34" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="M34" s="23"/>
-    </row>
-    <row r="35" ht="16.5" customHeight="1">
-      <c r="C35" s="29" t="s">
+      <c r="M34" s="20"/>
+    </row>
+    <row r="35" spans="3:14" ht="16.5" customHeight="1">
+      <c r="C35" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="E35" s="30" t="s">
+      <c r="E35" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="I35" s="30" t="s">
+      <c r="I35" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="L35" s="19" t="s">
+      <c r="L35" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M35" s="23"/>
-    </row>
-    <row r="36" ht="16.5" customHeight="1">
-      <c r="C36" s="31"/>
-      <c r="E36" s="22"/>
-      <c r="I36" s="22"/>
-      <c r="L36" s="19"/>
-      <c r="M36" s="23"/>
-    </row>
-    <row r="37" ht="16.5" customHeight="1">
-      <c r="C37" s="31" t="s">
+      <c r="M35" s="20"/>
+    </row>
+    <row r="36" spans="3:14" ht="16.5" customHeight="1">
+      <c r="C36" s="28"/>
+      <c r="E36" s="19"/>
+      <c r="I36" s="19"/>
+      <c r="L36" s="16"/>
+      <c r="M36" s="20"/>
+    </row>
+    <row r="37" spans="3:14" ht="16.5" customHeight="1">
+      <c r="C37" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="E37" s="22"/>
-      <c r="I37" s="22"/>
-      <c r="L37" s="19"/>
-      <c r="M37" s="23"/>
-    </row>
-    <row r="38" ht="16.5" customHeight="1">
-      <c r="C38" s="28" t="s">
+      <c r="E37" s="19"/>
+      <c r="I37" s="19"/>
+      <c r="L37" s="16"/>
+      <c r="M37" s="20"/>
+    </row>
+    <row r="38" spans="3:14" ht="16.5" customHeight="1">
+      <c r="C38" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="E38" s="23" t="s">
+      <c r="E38" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="I38" s="23" t="s">
+      <c r="I38" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="L38" s="32" t="s">
+      <c r="L38" s="29" t="s">
         <v>60</v>
       </c>
-      <c r="N38" s="23"/>
-    </row>
-    <row r="39" ht="16.5" customHeight="1">
-      <c r="C39" s="29" t="s">
+      <c r="N38" s="20"/>
+    </row>
+    <row r="39" spans="3:14" ht="16.5" customHeight="1">
+      <c r="C39" s="26" t="s">
         <v>61</v>
       </c>
-      <c r="E39" s="30" t="s">
+      <c r="E39" s="27" t="s">
         <v>62</v>
       </c>
-      <c r="I39" s="30" t="s">
+      <c r="I39" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="L39" s="30" t="s">
+      <c r="L39" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="N39" s="23"/>
-    </row>
-    <row r="40" ht="16.5" customHeight="1">
-      <c r="C40" s="29" t="s">
+      <c r="N39" s="20"/>
+    </row>
+    <row r="40" spans="3:14" ht="16.5" customHeight="1">
+      <c r="C40" s="26" t="s">
         <v>65</v>
       </c>
-      <c r="E40" s="30" t="s">
+      <c r="E40" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="I40" s="30" t="s">
+      <c r="I40" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="L40" s="19" t="s">
+      <c r="L40" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="N40" s="23"/>
-    </row>
-    <row r="41" ht="16.5" customHeight="1">
-      <c r="C41" s="29" t="s">
+      <c r="N40" s="20"/>
+    </row>
+    <row r="41" spans="3:14" ht="16.5" customHeight="1">
+      <c r="C41" s="26" t="s">
         <v>68</v>
       </c>
-      <c r="E41" s="30" t="s">
+      <c r="E41" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="G41" s="23"/>
-      <c r="I41" s="9" t="s">
+      <c r="G41" s="20"/>
+      <c r="I41" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="J41" s="23"/>
-      <c r="L41" s="33" t="s">
+      <c r="J41" s="20"/>
+      <c r="L41" s="30" t="s">
         <v>71</v>
       </c>
-      <c r="N41" s="23"/>
-    </row>
-    <row r="42" ht="16.5" customHeight="1">
-      <c r="C42" s="26"/>
-      <c r="D42" s="23"/>
-      <c r="F42" s="23"/>
-      <c r="J42" s="23"/>
-      <c r="L42" s="19"/>
-      <c r="N42" s="23"/>
-    </row>
-    <row r="43" ht="16.5" customHeight="1">
-      <c r="C43" s="27" t="s">
+      <c r="N41" s="20"/>
+    </row>
+    <row r="42" spans="3:14" ht="16.5" customHeight="1">
+      <c r="C42" s="23"/>
+      <c r="D42" s="20"/>
+      <c r="F42" s="20"/>
+      <c r="J42" s="20"/>
+      <c r="L42" s="16"/>
+      <c r="N42" s="20"/>
+    </row>
+    <row r="43" spans="3:14" ht="16.5" customHeight="1">
+      <c r="C43" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="L43" s="19"/>
-    </row>
-    <row r="44" ht="16.5" customHeight="1">
-      <c r="C44" s="28" t="s">
+      <c r="L43" s="16"/>
+    </row>
+    <row r="44" spans="3:14" ht="16.5" customHeight="1">
+      <c r="C44" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="E44" s="23" t="s">
+      <c r="E44" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="I44" s="23" t="s">
+      <c r="I44" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="L44" s="20" t="s">
+      <c r="L44" s="17" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="45" ht="16.5" customHeight="1">
-      <c r="C45" s="29" t="s">
+    <row r="45" spans="3:14" ht="16.5" customHeight="1">
+      <c r="C45" s="26" t="s">
         <v>73</v>
       </c>
-      <c r="E45" s="30" t="s">
+      <c r="E45" s="27" t="s">
         <v>74</v>
       </c>
-      <c r="I45" s="30" t="s">
+      <c r="I45" s="27" t="s">
         <v>75</v>
       </c>
-      <c r="L45" s="19" t="s">
+      <c r="L45" s="16" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="46" ht="16.5" customHeight="1">
-      <c r="C46" s="29" t="s">
+    <row r="46" spans="3:14" ht="16.5" customHeight="1">
+      <c r="C46" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="E46" s="30" t="s">
+      <c r="E46" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="I46" s="30" t="s">
+      <c r="I46" s="27" t="s">
         <v>78</v>
       </c>
-      <c r="L46" s="19" t="s">
+      <c r="L46" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="N46" s="30"/>
-    </row>
-    <row r="47" ht="16.5" customHeight="1">
-      <c r="C47" s="26"/>
-      <c r="L47" s="19"/>
-    </row>
-    <row r="48" ht="16.5" customHeight="1">
-      <c r="C48" s="27" t="s">
+      <c r="N46" s="27"/>
+    </row>
+    <row r="47" spans="3:14" ht="16.5" customHeight="1">
+      <c r="C47" s="23"/>
+      <c r="L47" s="16"/>
+    </row>
+    <row r="48" spans="3:14" ht="16.5" customHeight="1">
+      <c r="C48" s="24" t="s">
         <v>79</v>
       </c>
-      <c r="L48" s="19"/>
-    </row>
-    <row r="49" ht="16.5" customHeight="1">
-      <c r="C49" s="28" t="s">
+      <c r="L48" s="16"/>
+    </row>
+    <row r="49" spans="1:12" ht="16.5" customHeight="1">
+      <c r="C49" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="E49" s="23" t="s">
+      <c r="E49" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="I49" s="23" t="s">
+      <c r="I49" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="L49" s="20" t="s">
+      <c r="L49" s="17" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="50" ht="16.5" customHeight="1">
-      <c r="C50" s="34" t="s">
+    <row r="50" spans="1:12" ht="16.5" customHeight="1">
+      <c r="C50" s="31" t="s">
         <v>80</v>
       </c>
-      <c r="D50" s="35"/>
-      <c r="E50" s="36" t="s">
+      <c r="D50" s="32"/>
+      <c r="E50" s="33" t="s">
         <v>81</v>
       </c>
-      <c r="F50" s="35"/>
-      <c r="G50" s="35"/>
-      <c r="H50" s="35"/>
-      <c r="I50" s="35" t="s">
+      <c r="F50" s="32"/>
+      <c r="G50" s="32"/>
+      <c r="H50" s="32"/>
+      <c r="I50" s="32" t="s">
         <v>82</v>
       </c>
-      <c r="J50" s="35"/>
-      <c r="K50" s="35"/>
-      <c r="L50" s="37" t="s">
+      <c r="J50" s="32"/>
+      <c r="K50" s="32"/>
+      <c r="L50" s="34" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="52" ht="16.5" customHeight="1">
-      <c r="B52" s="9" t="s">
+    <row r="52" spans="1:12" ht="16.5" customHeight="1">
+      <c r="B52" s="6" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="53" ht="16.5" customHeight="1">
-      <c r="B53" s="9" t="s">
+    <row r="53" spans="1:12" ht="16.5" customHeight="1">
+      <c r="B53" s="6" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="54" ht="16.5" customHeight="1">
-      <c r="B54" s="9" t="s">
+    <row r="54" spans="1:12" ht="16.5" customHeight="1">
+      <c r="B54" s="6" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="56" ht="16.5" customHeight="1">
-      <c r="B56" s="9" t="s">
+    <row r="56" spans="1:12" ht="16.5" customHeight="1">
+      <c r="B56" s="6" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="57" ht="16.5" customHeight="1">
-      <c r="B57" s="9" t="s">
+    <row r="57" spans="1:12" ht="16.5" customHeight="1">
+      <c r="B57" s="6" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="58" ht="16.5" customHeight="1">
-      <c r="B58" s="9" t="s">
+    <row r="58" spans="1:12" ht="16.5" customHeight="1">
+      <c r="B58" s="6" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="59" ht="16.5" customHeight="1">
-      <c r="A59" s="9" t="s">
+    <row r="59" spans="1:12" ht="16.5" customHeight="1">
+      <c r="A59" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="E59" s="11" t="s">
+      <c r="E59" s="8" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="60" ht="16.5" customHeight="1">
-      <c r="B60" s="38" t="s">
+    <row r="60" spans="1:12" ht="16.5" customHeight="1">
+      <c r="B60" s="35" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="61" ht="16.5" customHeight="1">
-      <c r="B61" s="9" t="s">
+    <row r="61" spans="1:12" ht="16.5" customHeight="1">
+      <c r="B61" s="6" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="62" ht="16.5" customHeight="1">
-      <c r="B62" s="9" t="s">
+    <row r="62" spans="1:12" ht="16.5" customHeight="1">
+      <c r="B62" s="6" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="63" ht="16.5" customHeight="1">
-      <c r="B63" s="9" t="s">
+    <row r="63" spans="1:12" ht="16.5" customHeight="1">
+      <c r="B63" s="6" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="64" ht="16.5" customHeight="1">
-      <c r="B64" s="9" t="s">
+    <row r="64" spans="1:12" ht="16.5" customHeight="1">
+      <c r="B64" s="6" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="66" ht="16.5" customHeight="1">
-      <c r="A66" s="10" t="s">
+    <row r="66" spans="1:6" ht="16.5" customHeight="1">
+      <c r="A66" s="7" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="67" ht="16.5" customHeight="1">
-      <c r="B67" s="38" t="s">
+    <row r="67" spans="1:6" ht="16.5" customHeight="1">
+      <c r="B67" s="35" t="s">
         <v>96</v>
       </c>
-      <c r="E67" s="11" t="s">
+      <c r="E67" s="8" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="69" ht="16.5" customHeight="1">
-      <c r="A69" s="10" t="s">
+    <row r="69" spans="1:6" ht="16.5" customHeight="1">
+      <c r="A69" s="7" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="70" ht="16.5" customHeight="1">
-      <c r="B70" s="39" t="s">
+    <row r="70" spans="1:6" ht="16.5" customHeight="1">
+      <c r="B70" s="36" t="s">
         <v>98</v>
       </c>
-      <c r="C70" s="39"/>
-      <c r="D70" s="39"/>
-      <c r="E70" s="40" t="s">
+      <c r="C70" s="36"/>
+      <c r="D70" s="36"/>
+      <c r="E70" s="37" t="s">
         <v>99</v>
       </c>
-      <c r="F70" s="40"/>
-    </row>
-    <row r="71" ht="16.5" customHeight="1">
-      <c r="B71" s="9" t="s">
+      <c r="F70" s="37"/>
+    </row>
+    <row r="71" spans="1:6" ht="16.5" customHeight="1">
+      <c r="B71" s="6" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="72" ht="16.5" customHeight="1">
-      <c r="B72" s="9" t="s">
+    <row r="72" spans="1:6" ht="16.5" customHeight="1">
+      <c r="B72" s="6" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="73" ht="16.5" customHeight="1">
-      <c r="B73" s="9" t="s">
+    <row r="73" spans="1:6" ht="16.5" customHeight="1">
+      <c r="B73" s="6" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="74" ht="16.5" customHeight="1">
-      <c r="B74" s="9" t="s">
+    <row r="74" spans="1:6" ht="16.5" customHeight="1">
+      <c r="B74" s="6" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="77" ht="16.5" customHeight="1">
-      <c r="A77" s="38"/>
+    <row r="77" spans="1:6" ht="16.5" customHeight="1">
+      <c r="A77" s="35"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -2048,181 +1994,122 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F1E1092-59D6-0841-9542-AE5505D0AA25}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.9990234375" defaultRowHeight="16.5" customHeight="1"/>
+  <dimension ref="A2:E36"/>
+  <sheetFormatPr defaultColWidth="10" defaultRowHeight="16.5" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="16.5" customHeight="1">
-      <c r="A2" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="E2" s="8"/>
-    </row>
-    <row r="3" ht="16.5" customHeight="1">
-      <c r="A3" s="7"/>
-      <c r="B3" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="E3" s="8"/>
-    </row>
-    <row r="4" ht="16.5" customHeight="1">
-      <c r="A4" s="7"/>
-      <c r="B4" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="E4" s="8"/>
-    </row>
-    <row r="5" ht="16.5" customHeight="1">
-      <c r="A5" s="7"/>
-      <c r="B5" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="E5" s="8"/>
-    </row>
-    <row r="6" ht="16.5" customHeight="1">
-      <c r="A6" s="7"/>
-      <c r="B6" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="E6" s="8"/>
-    </row>
-    <row r="7" ht="16.5" customHeight="1">
-      <c r="A7" s="7"/>
-      <c r="E7" s="8"/>
-    </row>
-    <row r="8" ht="16.5" customHeight="1">
-      <c r="A8" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9" ht="16.5" customHeight="1">
-      <c r="A9" s="4" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="10" ht="16.5" customHeight="1">
-      <c r="A10" s="4" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="12" ht="16.5" customHeight="1">
-      <c r="A12" s="4" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="13" ht="16.5" customHeight="1">
-      <c r="A13" s="4" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="14" ht="16.5" customHeight="1">
-      <c r="A14" s="4" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="15" ht="16.5" customHeight="1">
-      <c r="A15" s="4" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="16" ht="16.5" customHeight="1">
-      <c r="A16" s="4" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="17" ht="16.5" customHeight="1">
-      <c r="A17" s="4" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="19" ht="16.5" customHeight="1">
-      <c r="A19" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="20" ht="16.5" customHeight="1">
-      <c r="A20" s="4" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="21" ht="16.5" customHeight="1">
-      <c r="A21" s="4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="22" ht="16.5" customHeight="1">
-      <c r="A22" s="4" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="23" ht="16.5" customHeight="1">
-      <c r="B23" s="4" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="24" ht="16.5" customHeight="1">
-      <c r="B24" s="4" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="25" ht="16.5" customHeight="1">
-      <c r="B25" s="4" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="26" ht="16.5" customHeight="1">
-      <c r="A26" s="4" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="28" ht="16.5" customHeight="1">
-      <c r="A28" s="4" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="29" ht="16.5" customHeight="1">
-      <c r="B29" s="4" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="30" ht="16.5" customHeight="1">
-      <c r="B30" s="4" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="31" ht="16.5" customHeight="1">
-      <c r="B31" s="4" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="32" ht="16.5" customHeight="1">
-      <c r="B32" s="4" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="34" ht="16.5" customHeight="1">
-      <c r="A34" s="4" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="35" ht="16.5" customHeight="1">
-      <c r="B35" s="4" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="36" ht="16.5" customHeight="1">
-      <c r="B36" s="4" t="s">
-        <v>133</v>
-      </c>
+    <row r="2" spans="1:5" ht="16.5" customHeight="1">
+      <c r="A2" s="4"/>
+      <c r="B2" s="40" t="s">
+        <v>144</v>
+      </c>
+      <c r="E2" s="5"/>
+    </row>
+    <row r="3" spans="1:5" ht="16.5" customHeight="1">
+      <c r="A3" s="4"/>
+      <c r="B3" s="1"/>
+      <c r="E3" s="5"/>
+    </row>
+    <row r="4" spans="1:5" ht="16.5" customHeight="1">
+      <c r="A4" s="4"/>
+      <c r="B4" s="1"/>
+      <c r="E4" s="5"/>
+    </row>
+    <row r="5" spans="1:5" ht="16.5" customHeight="1">
+      <c r="A5" s="4"/>
+      <c r="B5" s="1"/>
+      <c r="E5" s="5"/>
+    </row>
+    <row r="6" spans="1:5" ht="16.5" customHeight="1">
+      <c r="A6" s="4"/>
+      <c r="B6" s="1"/>
+      <c r="E6" s="5"/>
+    </row>
+    <row r="7" spans="1:5" ht="16.5" customHeight="1">
+      <c r="A7" s="4"/>
+      <c r="E7" s="5"/>
+    </row>
+    <row r="8" spans="1:5" ht="16.5" customHeight="1">
+      <c r="A8" s="4"/>
+      <c r="E8" s="5"/>
+    </row>
+    <row r="9" spans="1:5" ht="16.5" customHeight="1">
+      <c r="A9" s="1"/>
+    </row>
+    <row r="10" spans="1:5" ht="16.5" customHeight="1">
+      <c r="A10" s="1"/>
+    </row>
+    <row r="12" spans="1:5" ht="16.5" customHeight="1">
+      <c r="A12" s="1"/>
+    </row>
+    <row r="13" spans="1:5" ht="16.5" customHeight="1">
+      <c r="A13" s="1"/>
+    </row>
+    <row r="14" spans="1:5" ht="16.5" customHeight="1">
+      <c r="A14" s="1"/>
+    </row>
+    <row r="15" spans="1:5" ht="16.5" customHeight="1">
+      <c r="A15" s="1"/>
+    </row>
+    <row r="16" spans="1:5" ht="16.5" customHeight="1">
+      <c r="A16" s="1"/>
+    </row>
+    <row r="17" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A17" s="1"/>
+    </row>
+    <row r="19" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A19" s="1"/>
+    </row>
+    <row r="20" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A20" s="1"/>
+    </row>
+    <row r="21" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A21" s="1"/>
+    </row>
+    <row r="22" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A22" s="1"/>
+    </row>
+    <row r="23" spans="1:2" ht="16.5" customHeight="1">
+      <c r="B23" s="1"/>
+    </row>
+    <row r="24" spans="1:2" ht="16.5" customHeight="1">
+      <c r="B24" s="1"/>
+    </row>
+    <row r="25" spans="1:2" ht="16.5" customHeight="1">
+      <c r="B25" s="1"/>
+    </row>
+    <row r="26" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A26" s="1"/>
+    </row>
+    <row r="28" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A28" s="1"/>
+    </row>
+    <row r="29" spans="1:2" ht="16.5" customHeight="1">
+      <c r="B29" s="1"/>
+    </row>
+    <row r="30" spans="1:2" ht="16.5" customHeight="1">
+      <c r="B30" s="1"/>
+    </row>
+    <row r="31" spans="1:2" ht="16.5" customHeight="1">
+      <c r="B31" s="1"/>
+    </row>
+    <row r="32" spans="1:2" ht="16.5" customHeight="1">
+      <c r="B32" s="1"/>
+    </row>
+    <row r="34" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A34" s="1"/>
+    </row>
+    <row r="35" spans="1:2" ht="16.5" customHeight="1">
+      <c r="B35" s="1"/>
+    </row>
+    <row r="36" spans="1:2" ht="16.5" customHeight="1">
+      <c r="B36" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -2231,226 +2118,227 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F1E1092-59D6-0841-9542-AE5505D0AA25}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.9990234375" defaultRowHeight="16.5" customHeight="1"/>
+  <dimension ref="A1:B46"/>
+  <sheetFormatPr defaultColWidth="10" defaultRowHeight="16.5" customHeight="1"/>
   <sheetData>
-    <row r="1" ht="16.5" customHeight="1">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A1" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A2" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A3" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="16.5" customHeight="1">
+      <c r="B4" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="16.5" customHeight="1">
+      <c r="B5" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="16.5" customHeight="1">
+      <c r="B6" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="16.5" customHeight="1">
+      <c r="B7" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="16.5" customHeight="1">
+      <c r="B8" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="16.5" customHeight="1">
+      <c r="B10" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="16.5" customHeight="1">
+      <c r="B11" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="16.5" customHeight="1">
+      <c r="B12" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="16.5" customHeight="1">
+      <c r="B13" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="16.5" customHeight="1">
+      <c r="B14" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A15" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="16.5" customHeight="1">
+      <c r="B16" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="16.5" customHeight="1">
+      <c r="B17" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="16.5" customHeight="1">
+      <c r="B18" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="16.5" customHeight="1">
+      <c r="B19" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A21" s="4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A22" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A23" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="16.5" customHeight="1">
+      <c r="B24" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="16.5" customHeight="1">
+      <c r="B25" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="16.5" customHeight="1">
+      <c r="B26" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A28" s="4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A29" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A30" s="4"/>
+      <c r="B30" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A31" s="4"/>
+      <c r="B31" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A32" s="4"/>
+      <c r="B32" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A33" s="4"/>
+      <c r="B33" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A34" s="4"/>
+      <c r="B34" s="1" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="2" ht="16.5" customHeight="1">
-      <c r="A2" s="6" t="s">
+    <row r="35" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A35" s="4"/>
+    </row>
+    <row r="36" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A36" s="1" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="3" ht="16.5" customHeight="1">
-      <c r="A3" s="4" t="s">
+    <row r="37" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A37" s="4"/>
+    </row>
+    <row r="38" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A38" s="4" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="4" ht="16.5" customHeight="1">
-      <c r="B4" s="4" t="s">
+    <row r="39" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A39" s="1" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="5" ht="16.5" customHeight="1">
-      <c r="B5" s="4" t="s">
+    <row r="40" spans="1:2" ht="16.5" customHeight="1">
+      <c r="B40" s="1" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="6" ht="16.5" customHeight="1">
-      <c r="B6" s="4" t="s">
+    <row r="41" spans="1:2" ht="16.5" customHeight="1">
+      <c r="B41" s="1" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="7" ht="16.5" customHeight="1">
-      <c r="B7" s="4" t="s">
+    <row r="42" spans="1:2" ht="16.5" customHeight="1">
+      <c r="B42" s="1" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="8" ht="16.5" customHeight="1">
-      <c r="B8" s="4" t="s">
+    <row r="43" spans="1:2" ht="16.5" customHeight="1">
+      <c r="B43" s="1" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="10" ht="16.5" customHeight="1">
-      <c r="B10" s="4" t="s">
+    <row r="44" spans="1:2" ht="16.5" customHeight="1">
+      <c r="B44" s="1" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="11" ht="16.5" customHeight="1">
-      <c r="B11" s="4" t="s">
+    <row r="46" spans="1:2" ht="16.5" customHeight="1">
+      <c r="A46" s="1" t="s">
         <v>143</v>
-      </c>
-    </row>
-    <row r="12" ht="16.5" customHeight="1">
-      <c r="B12" s="4" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="13" ht="16.5" customHeight="1">
-      <c r="B13" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="14" ht="16.5" customHeight="1">
-      <c r="B14" s="4" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="15" ht="16.5" customHeight="1">
-      <c r="A15" s="4" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="16" ht="16.5" customHeight="1">
-      <c r="B16" s="4" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="17" ht="16.5" customHeight="1">
-      <c r="B17" s="4" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="18" ht="16.5" customHeight="1">
-      <c r="B18" s="4" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="19" ht="16.5" customHeight="1">
-      <c r="B19" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="21" ht="16.5" customHeight="1">
-      <c r="A21" s="7" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="22" ht="16.5" customHeight="1">
-      <c r="A22" s="4" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="23" ht="16.5" customHeight="1">
-      <c r="A23" s="4" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="24" ht="16.5" customHeight="1">
-      <c r="B24" s="4" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="25" ht="16.5" customHeight="1">
-      <c r="B25" s="4" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="26" ht="16.5" customHeight="1">
-      <c r="B26" s="4" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="28" ht="16.5" customHeight="1">
-      <c r="A28" s="7" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="29" ht="16.5" customHeight="1">
-      <c r="A29" s="4" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="30" ht="16.5" customHeight="1">
-      <c r="A30" s="7"/>
-      <c r="B30" s="4" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="31" ht="16.5" customHeight="1">
-      <c r="A31" s="7"/>
-      <c r="B31" s="4" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="32" ht="16.5" customHeight="1">
-      <c r="A32" s="7"/>
-      <c r="B32" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="33" ht="16.5" customHeight="1">
-      <c r="A33" s="7"/>
-      <c r="B33" s="4" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="34" ht="16.5" customHeight="1">
-      <c r="A34" s="7"/>
-      <c r="B34" s="4" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="35" ht="16.5" customHeight="1">
-      <c r="A35" s="7"/>
-    </row>
-    <row r="36" ht="16.5" customHeight="1">
-      <c r="A36" s="4" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="37" ht="16.5" customHeight="1">
-      <c r="A37" s="7"/>
-    </row>
-    <row r="38" ht="16.5" customHeight="1">
-      <c r="A38" s="7" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="39" ht="16.5" customHeight="1">
-      <c r="A39" s="4" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="40" ht="16.5" customHeight="1">
-      <c r="B40" s="4" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="41" ht="16.5" customHeight="1">
-      <c r="B41" s="4" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="42" ht="16.5" customHeight="1">
-      <c r="B42" s="4" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="43" ht="16.5" customHeight="1">
-      <c r="B43" s="4" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="44" ht="16.5" customHeight="1">
-      <c r="B44" s="4" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="46" ht="16.5" customHeight="1">
-      <c r="A46" s="4" t="s">
-        <v>173</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>